--- a/sample_sov_cleaned.xlsx
+++ b/sample_sov_cleaned.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cleaned Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source References" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,8 +540,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -635,8 +638,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -731,8 +736,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -827,8 +834,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -870,27 +879,19 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>1995</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>8000</v>
       </c>
-      <c r="M5" t="n">
-        <v>1200000</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>800000</v>
       </c>
       <c r="O5" t="n">
         <v>400000</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>2400000</v>
       </c>
@@ -918,13 +919,13 @@
       <c r="W5" t="n">
         <v>32.7767</v>
       </c>
-      <c r="X5" t="n">
-        <v>-96.797</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -985,7 +986,7 @@
         <v>25000000</v>
       </c>
       <c r="P6" t="n">
-        <v>5000000</v>
+        <v>-5000</v>
       </c>
       <c r="Q6" t="n">
         <v>125000000</v>
@@ -1019,8 +1020,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1115,8 +1118,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1173,12 +1178,8 @@
       <c r="N8" t="n">
         <v>3000000</v>
       </c>
-      <c r="O8" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>14000000</v>
       </c>
@@ -1211,8 +1212,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1304,6 +1307,1118 @@
       </c>
       <c r="X9" t="n">
         <v>-93.265</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>location_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>occupancy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>num_stories</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>square_footage</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>building_value</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>contents_value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>bi_value</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>other_value</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tiv</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>flood_zone</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>earthquake_zone</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sprinklered</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>policy_limit</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>deductible</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M4</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N4</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O4</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P4</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W5</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M6</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O6</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P6</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S6</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W6</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M7</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O7</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P7</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W7</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M8</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O8</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R8</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V8</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W8</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L9</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M9</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O9</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q9</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S9</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T9</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V9</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W9</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q10</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S10</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T10</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V10</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W10</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K11</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L11</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M11</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O11</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P11</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q11</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R11</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S11</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T11</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U11</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V11</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W11</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X11</t>
+        </is>
       </c>
     </row>
   </sheetData>
